--- a/output/pdf_financials_xlsx/WDO.xlsx
+++ b/output/pdf_financials_xlsx/WDO.xlsx
@@ -2398,13 +2398,13 @@
         <v>33.185</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>41.371</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>123.097</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>353.865</v>
       </c>
     </row>
     <row r="35">
@@ -2508,13 +2508,13 @@
         <v>34.145</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>2.646</v>
+        <v>44.017</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>4.206</v>
+        <v>127.303</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>353.865</v>
       </c>
     </row>
     <row r="37">
@@ -3168,13 +3168,13 @@
         <v>21.283</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>51.526</v>
+        <v>10.155</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>145.664</v>
+        <v>22.567</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>373.723</v>
+        <v>19.858</v>
       </c>
     </row>
     <row r="49">
@@ -7400,13 +7400,13 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-1.914</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-2.753</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-3.632</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
@@ -7455,13 +7455,13 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-1.914</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-2.753</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-3.632</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -41588,7 +41588,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -57932,7 +57936,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -61538,7 +61542,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -67058,7 +67062,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -70584,7 +70588,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">

--- a/output/pdf_financials_xlsx/WDO.xlsx
+++ b/output/pdf_financials_xlsx/WDO.xlsx
@@ -7492,10 +7492,10 @@
         <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>-1.995</v>
+        <v>-6.003</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>-1.995</v>
+        <v>-6.021</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>

--- a/output/pdf_financials_xlsx/WDO.xlsx
+++ b/output/pdf_financials_xlsx/WDO.xlsx
@@ -6502,10 +6502,10 @@
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>61.898</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -6526,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>0</v>
+        <v>-58.563</v>
       </c>
       <c r="N108" s="3" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-14.391</v>
       </c>
     </row>
     <row r="122">
@@ -28704,7 +28704,11 @@
           <t>Share repurchases 17</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -29760,7 +29764,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -32592,7 +32600,11 @@
           <t>Net income loss $</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -34966,7 +34978,11 @@
           <t>Reversal of impairment charges 15</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -43384,7 +43400,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -48292,7 +48312,11 @@
           <t>Impairment charges (Note 11)</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -54740,7 +54764,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E495" s="5" t="n">
         <v>-1.672</v>
       </c>
@@ -55962,7 +55990,11 @@
           <t>Proceeds on sale of marketable securites</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
